--- a/data/trans_camb/LAWTONB_2R3-Clase-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R3-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 23,24</t>
+          <t>-3,95; 23,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 7,81</t>
+          <t>-8,33; 8,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 3,91</t>
+          <t>-9,87; 4,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,79; 7,77</t>
+          <t>-30,82; 5,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 10,54</t>
+          <t>-25,98; 11,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,68; 5,77</t>
+          <t>-26,97; 6,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 11,95</t>
+          <t>-9,74; 12,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 6,64</t>
+          <t>-11,36; 6,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 2,31</t>
+          <t>-11,9; 2,97</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-73,4; 1077,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-90,26; 383,42</t>
+          <t>-86,47; 429,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-78,77; 237,41</t>
+          <t>-77,8; 277,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 143,48</t>
+          <t>-100,0; 113,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,31; 116,01</t>
+          <t>-85,5; 160,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,51; 79,85</t>
+          <t>-78,63; 78,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,53; 219,87</t>
+          <t>-72,13; 197,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,8; 133,8</t>
+          <t>-70,72; 129,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,74; 39,48</t>
+          <t>-69,11; 59,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 13,69</t>
+          <t>-14,34; 13,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 14,2</t>
+          <t>-11,49; 14,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 7,54</t>
+          <t>-14,76; 8,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 31,23</t>
+          <t>-27,34; 28,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,08; 31,56</t>
+          <t>-27,98; 34,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 10,51</t>
+          <t>-32,36; 12,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 14,37</t>
+          <t>-11,48; 13,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 13,83</t>
+          <t>-12,79; 12,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 6,63</t>
+          <t>-14,0; 6,29</t>
         </is>
       </c>
     </row>
@@ -999,22 +999,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-77,25; 300,51</t>
+          <t>-75,69; 278,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,54; 296,08</t>
+          <t>-66,19; 299,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,07; 167,62</t>
+          <t>-71,97; 169,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,86; 544,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-76,11; 174,11</t>
+          <t>-75,74; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,92; 203,32</t>
+          <t>-58,2; 212,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 189,32</t>
+          <t>-62,26; 162,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,57; 101,03</t>
+          <t>-58,42; 86,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 14,13</t>
+          <t>-5,51; 13,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 8,63</t>
+          <t>-9,56; 8,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 10,84</t>
+          <t>-4,86; 11,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 22,69</t>
+          <t>-17,12; 23,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 21,82</t>
+          <t>-18,49; 24,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 26,33</t>
+          <t>-12,33; 24,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 13,99</t>
+          <t>-3,87; 14,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 9,03</t>
+          <t>-7,78; 8,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 13,95</t>
+          <t>-1,73; 13,51</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 226,24</t>
+          <t>-37,76; 211,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,47; 160,37</t>
+          <t>-58,21; 149,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 177,81</t>
+          <t>-31,79; 216,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,27; 394,41</t>
+          <t>-55,33; 436,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,25; 319,34</t>
+          <t>-65,94; 405,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,04; 507,7</t>
+          <t>-36,82; 439,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 182,22</t>
+          <t>-26,09; 174,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,02; 129,61</t>
+          <t>-45,47; 98,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 191,95</t>
+          <t>-10,59; 183,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 19,83</t>
+          <t>3,93; 19,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 6,77</t>
+          <t>-6,51; 5,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 13,17</t>
+          <t>0,72; 12,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 24,95</t>
+          <t>-2,82; 25,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 17,48</t>
+          <t>-7,42; 18,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 4,96</t>
+          <t>-24,12; 4,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,97; 18,09</t>
+          <t>5,41; 18,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 7,85</t>
+          <t>-4,14; 7,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 7,43</t>
+          <t>-11,35; 7,05</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>24,13; 157,74</t>
+          <t>20,0; 154,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 54,99</t>
+          <t>-36,94; 47,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 109,19</t>
+          <t>3,38; 106,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,8; 232,74</t>
+          <t>-16,91; 272,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 180,66</t>
+          <t>-37,83; 189,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,18; 47,61</t>
+          <t>-90,14; 49,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,63; 135,58</t>
+          <t>29,33; 149,27</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 64,58</t>
+          <t>-24,15; 58,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-70,43; 53,2</t>
+          <t>-66,91; 50,7</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 20,62</t>
+          <t>-2,91; 20,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 20,96</t>
+          <t>0,52; 21,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 21,2</t>
+          <t>-0,96; 19,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 19,19</t>
+          <t>-5,61; 18,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 11,13</t>
+          <t>-13,22; 10,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 18,29</t>
+          <t>-2,01; 17,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 16,97</t>
+          <t>-0,44; 17,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 11,34</t>
+          <t>-5,99; 11,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 17,14</t>
+          <t>1,97; 17,07</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 338,69</t>
+          <t>-17,68; 322,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 365,8</t>
+          <t>-3,56; 354,79</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 388,57</t>
+          <t>-11,18; 326,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 105,2</t>
+          <t>-16,87; 104,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,17; 61,13</t>
+          <t>-40,53; 56,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 101,49</t>
+          <t>-5,24; 103,98</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 112,43</t>
+          <t>-3,26; 114,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 71,7</t>
+          <t>-21,85; 74,96</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2,57; 111,36</t>
+          <t>6,18; 110,92</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-96,53; 0,0</t>
+          <t>-75,71; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1767,37 +1767,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 85,13</t>
+          <t>-30,64; 84,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,08; 12,54</t>
+          <t>0,61; 13,17</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,61; 13,81</t>
+          <t>1,39; 13,64</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,07; 21,95</t>
+          <t>10,93; 21,78</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,95; 12,78</t>
+          <t>0,85; 12,2</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,43; 13,13</t>
+          <t>1,56; 13,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10,71; 21,65</t>
+          <t>11,42; 22,33</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5,11; 83,08</t>
+          <t>3,07; 90,02</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6,7; 91,5</t>
+          <t>6,75; 92,69</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>53,85; 149,92</t>
+          <t>51,97; 150,98</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,11; 85,43</t>
+          <t>3,83; 83,17</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7,15; 89,85</t>
+          <t>7,7; 91,66</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>50,43; 148,21</t>
+          <t>55,73; 150,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,18; 12,85</t>
+          <t>3,3; 12,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 6,14</t>
+          <t>-2,15; 5,73</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,34; 7,3</t>
+          <t>-0,35; 7,17</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,67; 12,25</t>
+          <t>2,89; 11,82</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,23; 9,35</t>
+          <t>-0,19; 9,41</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 11,29</t>
+          <t>-8,33; 10,73</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,81</t>
+          <t>4,4; 11,11</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,55; 7,05</t>
+          <t>0,75; 7,01</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 7,95</t>
+          <t>-4,66; 8,08</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>22,21; 119,71</t>
+          <t>20,35; 109,66</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 57,54</t>
+          <t>-14,4; 53,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1,4; 68,95</t>
+          <t>-2,1; 66,49</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12,5; 75,15</t>
+          <t>13,62; 73,76</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,48; 57,05</t>
+          <t>-1,14; 56,21</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,03; 64,75</t>
+          <t>-40,25; 60,38</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,08; 75,35</t>
+          <t>24,46; 76,05</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3,11; 48,91</t>
+          <t>3,77; 47,59</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 53,38</t>
+          <t>-26,26; 52,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/LAWTONB_2R3-Clase-trans_camb.xlsx
+++ b/data/trans_camb/LAWTONB_2R3-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,42</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,61</t>
+          <t>-9,18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,47</t>
+          <t>-3,68</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 23,77</t>
+          <t>-5,06; 22,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 8,49</t>
+          <t>-8,47; 7,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 4,22</t>
+          <t>-9,36; 3,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,82; 5,43</t>
+          <t>-29,52; 7,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 11,7</t>
+          <t>-28,5; 11,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 6,13</t>
+          <t>-27,15; 5,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 12,02</t>
+          <t>-9,62; 11,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 6,46</t>
+          <t>-11,56; 5,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 2,97</t>
+          <t>-11,95; 2,1</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-23,13%</t>
+          <t>-23,77%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-42,49%</t>
+          <t>-45,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-32,06%</t>
+          <t>-34,04%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-69,29; 1165,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-86,47; 429,11</t>
+          <t>-88,3; 297,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-77,8; 277,01</t>
+          <t>-78,93; 261,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 113,37</t>
+          <t>-100,0; 156,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,5; 160,8</t>
+          <t>-88,14; 136,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-78,63; 78,25</t>
+          <t>-79,45; 91,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,13; 197,91</t>
+          <t>-69,68; 199,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,72; 129,9</t>
+          <t>-74,79; 104,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,11; 59,56</t>
+          <t>-69,7; 37,54</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,29</t>
+          <t>-1,52</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,31</t>
+          <t>-6,03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,15</t>
+          <t>-2,16</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 13,32</t>
+          <t>-13,48; 15,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 14,5</t>
+          <t>-13,06; 14,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 8,0</t>
+          <t>-17,09; 7,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 28,64</t>
+          <t>-28,38; 31,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,98; 34,59</t>
+          <t>-29,94; 32,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 12,92</t>
+          <t>-34,84; 12,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 13,2</t>
+          <t>-10,65; 14,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 12,7</t>
+          <t>-12,35; 12,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 6,29</t>
+          <t>-13,69; 6,41</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-10,68%</t>
+          <t>-12,58%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-30,66%</t>
+          <t>-29,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-15,28%</t>
+          <t>-15,3%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-75,69; 278,99</t>
+          <t>-76,53; 357,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,19; 299,44</t>
+          <t>-66,38; 326,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,97; 169,4</t>
+          <t>-72,08; 166,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-82,86; 544,49</t>
+          <t>-80,87; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,74; —</t>
+          <t>-77,62; 220,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 212,19</t>
+          <t>-57,93; 213,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,26; 162,36</t>
+          <t>-57,63; 165,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 86,77</t>
+          <t>-58,59; 99,1</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>2,49</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>10,95</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,21</t>
+          <t>5,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 13,51</t>
+          <t>-5,6; 14,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 8,24</t>
+          <t>-7,95; 8,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 11,85</t>
+          <t>-6,98; 10,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 23,45</t>
+          <t>-16,47; 21,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 24,14</t>
+          <t>-20,25; 22,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 24,26</t>
+          <t>-11,34; 27,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 14,11</t>
+          <t>-5,44; 12,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 8,32</t>
+          <t>-7,81; 9,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 13,51</t>
+          <t>-2,6; 14,13</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-37,76; 211,47</t>
+          <t>-40,43; 257,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,21; 149,7</t>
+          <t>-52,77; 151,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,79; 216,26</t>
+          <t>-41,91; 182,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,33; 436,37</t>
+          <t>-53,83; 394,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,94; 405,32</t>
+          <t>-70,53; 429,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 439,0</t>
+          <t>-32,07; 540,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 174,01</t>
+          <t>-33,2; 159,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,47; 98,85</t>
+          <t>-40,77; 130,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 183,86</t>
+          <t>-15,58; 194,06</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>6,26</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,11</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,9</t>
+          <t>5,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 19,33</t>
+          <t>4,47; 20,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 5,82</t>
+          <t>-6,45; 5,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 12,94</t>
+          <t>0,22; 12,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 25,14</t>
+          <t>-2,97; 24,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 18,22</t>
+          <t>-6,51; 18,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 4,97</t>
+          <t>-5,89; 12,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 18,46</t>
+          <t>4,76; 18,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 7,36</t>
+          <t>-4,4; 6,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 7,05</t>
+          <t>-0,04; 10,22</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-53,92%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-12,6%</t>
+          <t>36,31%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,0; 154,78</t>
+          <t>24,61; 166,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,94; 47,33</t>
+          <t>-35,65; 48,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,38; 106,34</t>
+          <t>1,05; 102,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 272,08</t>
+          <t>-16,99; 274,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,83; 189,34</t>
+          <t>-33,15; 208,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,14; 49,88</t>
+          <t>-26,51; 134,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,33; 149,27</t>
+          <t>26,88; 142,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 58,97</t>
+          <t>-25,21; 54,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-66,91; 50,7</t>
+          <t>-2,18; 82,56</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10,62</t>
+          <t>9,89</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,41</t>
+          <t>8,45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9,89</t>
+          <t>9,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 20,56</t>
+          <t>-3,77; 20,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 21,15</t>
+          <t>0,68; 21,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 19,92</t>
+          <t>-1,84; 20,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 18,73</t>
+          <t>-5,47; 17,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 10,43</t>
+          <t>-12,55; 10,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 17,97</t>
+          <t>-2,01; 17,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 17,7</t>
+          <t>-0,15; 17,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 11,2</t>
+          <t>-4,92; 12,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 17,07</t>
+          <t>0,93; 16,39</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 322,02</t>
+          <t>-23,72; 314,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 354,79</t>
+          <t>0,07; 382,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 326,0</t>
+          <t>-13,16; 357,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 104,5</t>
+          <t>-15,16; 100,32</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-40,53; 56,98</t>
+          <t>-39,33; 58,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 103,98</t>
+          <t>-7,6; 93,42</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 114,28</t>
+          <t>-3,18; 115,74</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,85; 74,96</t>
+          <t>-19,21; 78,16</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6,18; 110,92</t>
+          <t>3,13; 105,45</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41,86</t>
+          <t>42,19</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,54</t>
+          <t>16,68</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16,8</t>
+          <t>16,93</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-75,71; 0,0</t>
+          <t>-96,53; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1767,37 +1767,37 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-30,64; 84,85</t>
+          <t>-29,46; 84,89</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,61; 13,17</t>
+          <t>1,36; 12,73</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,39; 13,64</t>
+          <t>1,34; 13,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,93; 21,78</t>
+          <t>11,23; 22,13</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,85; 12,2</t>
+          <t>0,89; 12,0</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1,56; 13,8</t>
+          <t>1,29; 13,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>11,42; 22,33</t>
+          <t>12,07; 22,12</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>166,86%</t>
+          <t>168,18%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3,07; 90,02</t>
+          <t>5,39; 85,91</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6,75; 92,69</t>
+          <t>5,71; 93,18</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>51,97; 150,98</t>
+          <t>56,8; 156,1</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,83; 83,17</t>
+          <t>3,49; 81,31</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7,7; 91,66</t>
+          <t>8,01; 93,02</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>55,73; 150,16</t>
+          <t>57,74; 149,47</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,03</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,08</t>
+          <t>9,86</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,14</t>
+          <t>6,75</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,3; 12,5</t>
+          <t>3,6; 12,66</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 5,73</t>
+          <t>-1,51; 6,02</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 7,17</t>
+          <t>-0,75; 6,45</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,89; 11,82</t>
+          <t>2,83; 12,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 9,41</t>
+          <t>0,18; 9,55</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 10,73</t>
+          <t>6,15; 13,5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,4; 11,11</t>
+          <t>4,4; 10,88</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,01</t>
+          <t>0,71; 7,0</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 8,08</t>
+          <t>3,9; 9,3</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>20,35; 109,66</t>
+          <t>23,27; 119,71</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 53,52</t>
+          <t>-10,41; 54,9</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 66,49</t>
+          <t>-5,1; 59,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13,62; 73,76</t>
+          <t>14,31; 75,88</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 56,21</t>
+          <t>0,8; 58,77</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-40,25; 60,38</t>
+          <t>29,02; 84,59</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,46; 76,05</t>
+          <t>24,47; 74,33</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3,77; 47,59</t>
+          <t>4,11; 47,93</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-26,26; 52,19</t>
+          <t>21,68; 64,92</t>
         </is>
       </c>
     </row>
